--- a/registro de supuestos/Registro_Supuestos_Overfore_v1.4.xlsx
+++ b/registro de supuestos/Registro_Supuestos_Overfore_v1.4.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Consolidado de decisiones de diseño del numeral 16.1, v1.0 (documento de trabajo interno) · Subdocumento 3 — Esquema de solución y alcance, v1.4 · Catálogo de requerimientos, v2.3</t>
+          <t>Consolidado de decisiones de diseño del numeral 16.1, v1.0 (documento de trabajo interno) · Subdocumento 3 — Esquema de solución y alcance, v1.4 · Catálogo de requerimientos, v2.4</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1.4 — 30 de agosto de 2026. Recategoriza el SUP-37, que estaba como umbral definido por el proponente y es un vacío de información del CLIENTE; deja el SUP-27 como única fuente de la meta de adopción del criterio n.º 14, que el RF-MIG-005 duplicaba con un umbral distinto; y alinea el SUP-21 con el cierre del desarrollo de la Etapa 2 en el mes 18 del Artículo 17.º. Reemplaza la v1.3.</t>
+          <t>1.4 — 30 de agosto de 2026. Recategoriza el SUP-37, que estaba como umbral definido por el proponente y es un vacío de información del CLIENTE; deja el SUP-27 como única fuente de la meta de adopción del criterio n.º 14, que el RF-MIG-005 duplicaba con un umbral distinto; y alinea el SUP-21 con el cierre del desarrollo de la Etapa 2 en el mes 18 del Artículo 17.º. Reemplaza la v1.3. Revisión de consistencia del 1 de septiembre de 2026: se alinean SUP-02, SUP-11 y SUP-13 con las exclusiones del apartado 3 del Subdocumento 3 v1.4 y se corrige la cita del catálogo.</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Recálculo retroactivo de doce meses contra los cierres históricos. Si la diferencia no queda explicada por punto de medición, se incorpora el factor de corrección por equipo y período en la Etapa 2.</t>
+          <t>Recálculo retroactivo de doce meses contra los cierres históricos. Si la diferencia no queda explicada por punto de medición, el CLIENTE dispone de la evidencia para solicitar el factor de corrección por equipo y período como cambio conforme al Artículo 72.º de las Bases Administrativas: está excluido del Contrato en ambas etapas (RF-PES-006).</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Medir en marcha blanca qué porcentaje de viajes queda marcado como borde: si es material, se evalúa prorrateo automático en la Etapa 2. Medir además la tasa de uso del botón; si el operador no lo usa, el diseño falló (criterio n.º 14).</t>
+          <t>Medir en marcha blanca qué porcentaje de viajes queda marcado como borde. Con esa evidencia el CLIENTE decide si solicita el prorrateo automático como cambio conforme al Artículo 72.º de las Bases Administrativas: está excluido del Contrato en ambas etapas (RF-CAR-008). Medir además la tasa de uso del botón; si el operador no lo usa, el diseño falló (criterio n.º 14).</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Sin biometría en portería en la Etapa 1: torniquete con lectura de credencial, validación documental de habilitación en línea y alerta anticipada de vencimientos. El préstamo de credenciales se aborda con detección analítica de patrones. La biometría queda diferida, sujeta a la mesa de diálogo laboral que gestiona el CLIENTE.</t>
+          <t>Sin biometría en portería en ninguna de las dos etapas: torniquete con lectura de credencial, validación documental de habilitación en línea y alerta anticipada de vencimientos. El préstamo de credenciales se aborda con detección analítica de patrones. La biometría queda excluida del Contrato en ambas etapas, incorporable como cambio conforme al Artículo 72.º de las Bases Administrativas si la mesa de diálogo laboral lo permite que gestiona el CLIENTE.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
